--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>26/07 01:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>50</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>40</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>28/07 01:20</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>55</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>40</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>40</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>35</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>30/07 18:45</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>45</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45863.08137282894</v>
+        <v>45863.08137282408</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | New Englan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New England Revolution – CF MontréalÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25/07 23:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+3,38%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45863.15386551098</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>25/07 23:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F27" t="n">
+        <v>2.95</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,142 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45863.15386551098</v>
+        <v>45863.15386550926</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Deportes T</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Deportes Tolima – Deportivo PereiraPrimera A (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>25/07 23:20</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+26,1%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45863.19533990383</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Arthur Caz</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Arthur Cazaux – Arthur RinderknechATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25/07 10:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45863.19533990383</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Gimnasia L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata – CA IndependienteLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+3,62%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45863.19533990383</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>25/07 23:20</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45863.19533990383</v>
+        <v>45863.1953399074</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>25/07 10:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.25</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45863.19533990383</v>
+        <v>45863.1953399074</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1709,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1729,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45863.19533990383</v>
+        <v>45863.1953399074</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 1 / DNB | FC Metalog</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FC Metaloglobus Bucuresti – ACS Petrolul 52Roumanie - Liga I</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1 / DNB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>25/07 16:45</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+2,85%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45863.22935945621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>25/07 16:45</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>4.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,142 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45863.22935945621</v>
+        <v>45863.22935945602</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 2.5 - aces1er participant | Camilo Ugo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Camilo Ugo Carabelli – Luciano DarderiATP - Umag</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25/07 16:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+5,55%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45863.27505288889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Houston Dy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Houston Dynamo – Los Angeles GalaxyÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>26/07 00:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+4,34%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45863.27505288889</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Arka Gdyni</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Arka Gdynia – RKS RadomiakPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>25/07 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+1,66%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45863.27505288889</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>25/07 16:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45863.27505288889</v>
+        <v>45863.27505289352</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>26/07 00:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45863.27505288889</v>
+        <v>45863.27505289352</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>25/07 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.58</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,97 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45863.27505288889</v>
+        <v>45863.27505289352</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | E.Raducanu</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>E.Raducanu – M.SakkariWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>25/07 16:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45863.30955414814</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 3.5 - break1er participant | Daniil Med</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev – Corentin MoutetATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>25/07 18:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>56,5%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+4,51%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45863.30955414814</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45863.30955414814</v>
+        <v>45863.30955414352</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>25/07 18:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F36" t="n">
+        <v>1.85</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,187 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45863.30955414814</v>
+        <v>45863.30955414352</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Csiksze</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FK Csikszereda Miercurea Ciuc – Rapid BucarestLiga 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>25/07 19:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+27,4%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45863.35611841852</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tatran Pre</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tatran Presov – Slovan BratislavaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>26/07 18:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45863.35611841852</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Moins que 11.52e participant | L Fernande</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L Fernandez – Taylo TownsendWTA Washington 2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 11.52e participant</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>25/07 18:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+5,22%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45863.35611841852</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | X - aces | Marie Bouz</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marie Bouzkova – Tereza ValentovaWTA - Prague</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25/07 13:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+3,53%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45863.35611841852</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>25/07 19:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>60</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45863.35611841852</v>
+        <v>45863.35611841435</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>40</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45863.35611841852</v>
+        <v>45863.35611841435</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>25/07 18:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45863.35611841852</v>
+        <v>45863.35611841435</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>25/07 13:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F40" t="n">
+        <v>4.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,142 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45863.35611841852</v>
+        <v>45863.35611841435</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mirassol – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+19,2%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45863.39442104383</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sport Recife – SantosBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+9,89%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45863.39442104383</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shanghai S</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua – Henan Songshan LongmenSuper League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27/07 11:35</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+7,80%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45863.39442104383</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.85</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45863.39442104383</v>
+        <v>45863.39442104167</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45863.39442104383</v>
+        <v>45863.39442104167</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,142 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45863.39442104383</v>
+        <v>45863.39442104167</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Frances TiafoeATP - Washington</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>25/07 23:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45863.43569912451</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – OFK BelgradeSuperLiga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>26/07 18:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+6,16%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45863.43569912451</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Viktori</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FC Viktoria Plzen – FK JablonecSynot League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26/07 15:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+2,54%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45863.43569912451</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -2311,10 +2311,8 @@
           <t>25/07 23:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45863.43569912451</v>
+        <v>45863.43569912037</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>45</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45863.43569912451</v>
+        <v>45863.43569912037</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45863.43569912451</v>
+        <v>45863.43569912037</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,141 @@
         <v>45863.43569912037</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Cruz Azul </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cruz Azul – LeonLiga MX</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>27/07 01:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+32,9%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45863.53405245264</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Queretaro </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Queretaro FC – Pumas UnamLiga MX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>26/07 01:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45863.53405245264</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | KS Cracovi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>KS Cracovia – Termalica Bruk-Bet NiecieczaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>25/07 16:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+2,67%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45863.53405245264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45863.53405245264</v>
+        <v>45863.5340524537</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>26/07 01:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45863.53405245264</v>
+        <v>45863.5340524537</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.48</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,97 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45863.53405245264</v>
+        <v>45863.5340524537</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 14.51re période2e équipe | Mali (F) –</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mali (F) – South SudanInternational - Afrocan (F)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 14.51re période2e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+5,26%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45863.56826666552</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 1 (−1.5)1er set | L Fernande</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>L Fernandez – Taylo TownsendWTA Washington 2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)1er set</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>25/07 18:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+4,32%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45863.56826666552</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45863.56826666552</v>
+        <v>45863.56826666667</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>25/07 18:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,52 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45863.56826666552</v>
+        <v>45863.56826666667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Metaloglob</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Metaloglobus Bucuresti – FC Petrolul PloiestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>25/07 16:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+28,2%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45863.59905903425</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>25/07 16:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>55</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,97 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45863.59905903425</v>
+        <v>45863.59905903935</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Ferencvaro</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ferencvaros – FC NoahLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+34,1%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45863.64315245253</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré1re équipe | Anvers – U</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Anvers – Union Saint-GilloiseBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>25/07 18:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+7,52%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45863.64315245253</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>60</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45863.64315245253</v>
+        <v>45863.6431524537</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>25/07 18:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.35</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,142 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45863.64315245253</v>
+        <v>45863.6431524537</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Malmo FF –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Malmo FF – Rigas Futbola SkolaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+29,7%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45863.68731993122</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Las Vegas </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces – Minnesota LynxUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>25/07 23:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45863.68731993122</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sport Recife – SantosBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+7,41%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45863.68731993122</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>60</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45863.68731993122</v>
+        <v>45863.68731993056</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>25/07 23:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>25</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45863.68731993122</v>
+        <v>45863.68731993056</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3.2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,97 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45863.68731993122</v>
+        <v>45863.68731993056</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Houston Dy</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Houston Dynamo – Los Angeles GalaxyÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>26/07 00:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>42,3%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45863.72428345692</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tirs2e équipe | New Englan</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New England Revolution – CF Montréal385076e7 États-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>25/07 23:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+7,18%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45863.72428345692</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>26/07 00:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.7</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45863.72428345692</v>
+        <v>45863.72428346065</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>25/07 23:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F59" t="n">
+        <v>1.72</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,142 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45863.72428345692</v>
+        <v>45863.72428346065</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | SK Sigma O</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SK Sigma Olomouc – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>26/07 15:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+4,43%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45863.77372140819</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt – StromsgodsetNorvège. Norvège - Eliteserien</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+4,28%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45863.77372140819</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mirassol – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+3,99%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45863.77372140819</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>40</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45863.77372140819</v>
+        <v>45863.77372141204</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45863.77372140819</v>
+        <v>45863.77372141204</v>
       </c>
     </row>
     <row r="62">
@@ -3089,10 +3085,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.85</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3105,7 +3099,52 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45863.77372140819</v>
+        <v>45863.77372141204</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Pachuca – </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pachuca – Mazatlan FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>26/07 23:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+2,45%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45863.80566593249</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45863.80566593249</v>
+        <v>45863.8056659375</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Racing Club – Estudiantes de La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>27/07 00:15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+2,72%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45863.85152761717</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>27/07 00:15</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>40</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,142 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45863.85152761717</v>
+        <v>45863.85152761574</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Sarmien</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CA Sarmiento – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>25/07 22:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+18,8%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45863.89039800071</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | New Englan</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New England Revolution – CF Montréal385076e7 États-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>25/07 23:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>44,8%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+6,68%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45863.89039800071</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vitoria BA – PalmeirasSérie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>03/08 23:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+5,13%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45863.89039800071</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>75</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45863.89039800071</v>
+        <v>45863.89039799768</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>25/07 23:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.38</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45863.89039800071</v>
+        <v>45863.89039799768</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>45</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,97 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45863.89039800071</v>
+        <v>45863.89039799768</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Club Sport</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Club Sportivo Luqueno – Nacional AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>29/07 21:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45863.93247938677</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | 1 - aces | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Frances TiafoeATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>25/07 23:40</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+4,29%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45863.93247938677</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-25.xlsx
+++ b/data/valuebets_database_2025-07-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>29/07 21:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>40</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45863.93247938677</v>
+        <v>45863.93247938657</v>
       </c>
     </row>
     <row r="69">
@@ -3388,10 +3386,8 @@
           <t>25/07 23:40</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="F69" t="n">
+        <v>1.15</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3404,7 +3400,97 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45863.93247938677</v>
+        <v>45863.93247938657</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mirassol – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>50,6%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+3,79%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45863.97418871883</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Tennis | Tie-break: Oui | Alexander </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Alexander Bublik – Arthur Cazaux385076e7 Kitzbuhel ATP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>26/07 12:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>43,1%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+3,44%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45863.97418871883</v>
       </c>
     </row>
   </sheetData>
